--- a/vendedores.xlsx
+++ b/vendedores.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lmacias\Desktop\RUTAS LÓGICAS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37A64AFF-9A52-4FBA-A433-CEB6A949037E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFC409AC-1FDB-4A9E-A46F-737948DC9D3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{51B1F3F5-CE97-489B-B588-CC9BCF707A89}"/>
   </bookViews>
   <sheets>
     <sheet name="vendedores" sheetId="1" r:id="rId1"/>
+    <sheet name="Hoja1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="141">
   <si>
     <t>ID_Vendedor</t>
   </si>
@@ -51,6 +52,414 @@
   </si>
   <si>
     <t>RAMIREZ GAMBOA JOSUE</t>
+  </si>
+  <si>
+    <t>Archivo de ventas</t>
+  </si>
+  <si>
+    <t>ONTIVEROS ARAUJO IRAM ELEAZAR</t>
+  </si>
+  <si>
+    <t>SIDA RAYGOZA IRIS SARAHI</t>
+  </si>
+  <si>
+    <t>MASCORRO ZAPATA EDGAR</t>
+  </si>
+  <si>
+    <t>GARCIA SOTO HEIDI GRACIELA</t>
+  </si>
+  <si>
+    <t>MEDINA VAZQUEZ ERIKA</t>
+  </si>
+  <si>
+    <t>CUADRAS CANO CARLOS ARMANDO</t>
+  </si>
+  <si>
+    <t>GOMEZ GONZALEZ MARVIN GEOVANNY</t>
+  </si>
+  <si>
+    <t>MOSTRADOR TIJUANA</t>
+  </si>
+  <si>
+    <t>C:\Users\lmacias\Desktop\PEDIDOS SUGERIDOS\VENTAS FERRETEROS_TERESITA.xlsx</t>
+  </si>
+  <si>
+    <t>C:\Users\lmacias\Desktop\PEDIDOS SUGERIDOS\VENTAS FERRETEROS.xlsx</t>
+  </si>
+  <si>
+    <t>PONCE LOMELI PEDRO ALEJANDRO</t>
+  </si>
+  <si>
+    <t>JIMENEZ CARRILLO CHRISTIAN EDUARDO</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ AGUIRRE JOSE</t>
+  </si>
+  <si>
+    <t>MOJICA CORTES FRANCISCO JAVIER</t>
+  </si>
+  <si>
+    <t>CABRERA GUTIERREZ ANGEL</t>
+  </si>
+  <si>
+    <t>FERNANDEZ SORIANO VICTOR ISIDRO</t>
+  </si>
+  <si>
+    <t>ESCOBAR AGUIRRE JUAN FRANCISCO</t>
+  </si>
+  <si>
+    <t>ORDOÑEZ GUIZAR JOSE GUADALUPE</t>
+  </si>
+  <si>
+    <t>RAMOS RUIZ YAZMIN GUADALUPE</t>
+  </si>
+  <si>
+    <t>INACTIVOS FERRETEROS OCCIDENTE</t>
+  </si>
+  <si>
+    <t>https://github.com/ISAACPRISA/WEB_PRISA2/blob/main/VENTAS%20FERRETEROS.xlsx</t>
+  </si>
+  <si>
+    <t>https://github.com/ISAACPRISA/WEB_PRISA2/blob/main/VENTAS%20FERRETEROS_TERESITA.xlsx</t>
+  </si>
+  <si>
+    <t>URL ventas</t>
+  </si>
+  <si>
+    <t>TRUJILLO RAMIREZ ALDO ENRIQUE</t>
+  </si>
+  <si>
+    <t>MUÑOZ VALADEZ FRANCISCO</t>
+  </si>
+  <si>
+    <t>VALENZUELA ARMANDO</t>
+  </si>
+  <si>
+    <t>QUINTERO LEON JOSE ELEAZAR</t>
+  </si>
+  <si>
+    <t>MANZANAREZ ALVAREZ HUGO ALBERTO</t>
+  </si>
+  <si>
+    <t>LIZAOLA VELEZ HECTOR RENE</t>
+  </si>
+  <si>
+    <t>CRUZ MADRIGAL MIGUEL ANGEL</t>
+  </si>
+  <si>
+    <t>ZUÑIGA RUIZ AMELIA MIROSLAVA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ MUÑOZ JORGE EDUARDO</t>
+  </si>
+  <si>
+    <t>LIMON URIBE FERNANDO</t>
+  </si>
+  <si>
+    <t>CERVANTES BARRAGAN BERENICE GUADALUPE</t>
+  </si>
+  <si>
+    <t>AGUILAR CEJA KARINA JANET</t>
+  </si>
+  <si>
+    <t>PALAFOX ORTIZ ANTONIA GABRIELA</t>
+  </si>
+  <si>
+    <t>AVIÑA SEPULVEDA LUCIA</t>
+  </si>
+  <si>
+    <t>BUENO MITRE JUAN CARLOS</t>
+  </si>
+  <si>
+    <t>MORENO HERNANDEZ FRANCISCO JAVIER</t>
+  </si>
+  <si>
+    <t>LOZA MENDEZ MIGUEL ALBERTO</t>
+  </si>
+  <si>
+    <t>VACANTE MICHOACAN</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ MARTINEZ MIGUEL ANGEL MOISES</t>
+  </si>
+  <si>
+    <t>ROBLES ROBLES CESAR ALEJANDRO</t>
+  </si>
+  <si>
+    <t>NAVARRO DE ALVA RAUL</t>
+  </si>
+  <si>
+    <t>ARREOLA CHAVEZ JOSE LUIS</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ PEÑA FRANCISCO JAVIER</t>
+  </si>
+  <si>
+    <t>ANDRADE ZAPATA ALDO DANIEL</t>
+  </si>
+  <si>
+    <t>ALATRISTE FUENTES MARCO ANTONIO</t>
+  </si>
+  <si>
+    <t>VACANTE CHIHUAHUA</t>
+  </si>
+  <si>
+    <t>LOYA ROBLEDO ANTONIO</t>
+  </si>
+  <si>
+    <t>FIERRO MARTINEZ JOSE</t>
+  </si>
+  <si>
+    <t>SANCHEZ MOJICA PAMELA</t>
+  </si>
+  <si>
+    <t>VACANTE LAGUNA</t>
+  </si>
+  <si>
+    <t>GOMEZ PEREZ EDUARDO</t>
+  </si>
+  <si>
+    <t>ZAMBRANO GONZALEZ ROBERTO</t>
+  </si>
+  <si>
+    <t>ESPIRITU TLATEMPA JAVIER</t>
+  </si>
+  <si>
+    <t>MEZA LEON JUAN</t>
+  </si>
+  <si>
+    <t>EUSTAQUIO CARMONA JESUS ALBERTO</t>
+  </si>
+  <si>
+    <t>SOLORIO VILLASEÑOR ALEJANDRO</t>
+  </si>
+  <si>
+    <t>CARRILLO CONTRERAS HILARIO ANGEL</t>
+  </si>
+  <si>
+    <t>ACOSTA FLORES RODRIGO</t>
+  </si>
+  <si>
+    <t>CASTELLANOS MARRON EDGAR FERNANDO</t>
+  </si>
+  <si>
+    <t>MARTINEZ VARGAS JAVIER</t>
+  </si>
+  <si>
+    <t>HERNANDEZ CARMONA EDGAR GABRIEL</t>
+  </si>
+  <si>
+    <t>MENDOZA PERDOMO ALFREDO</t>
+  </si>
+  <si>
+    <t>CORDOVA RODRIGUEZ ALAN</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ HURTADO FELIPE</t>
+  </si>
+  <si>
+    <t>ROSALES SANCHEZ CINTHYA PAOLA</t>
+  </si>
+  <si>
+    <t>NAVA YAÑEZ LORENZO DE JESUS</t>
+  </si>
+  <si>
+    <t>SANTA ANA LOPEZ JESUS ENRIQUE</t>
+  </si>
+  <si>
+    <t>RAMIREZ HERNANDEZ LUIS FERNANDO</t>
+  </si>
+  <si>
+    <t>SALDAÑA PADILLA MANUEL</t>
+  </si>
+  <si>
+    <t>CASTAÑEDA HUITRADO JOSE MANUEL</t>
+  </si>
+  <si>
+    <t>CEDI OCOTLAN</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ LUJAN RUBEN EDUARDO</t>
+  </si>
+  <si>
+    <t>DIRECCION GENERAL</t>
+  </si>
+  <si>
+    <t>MARTINEZ DIAZ KATIA DANIELA</t>
+  </si>
+  <si>
+    <t>CALDERON MUÑIZ OMAR TOATZIN</t>
+  </si>
+  <si>
+    <t>RAMIREZ BARRON JUAN PABLO</t>
+  </si>
+  <si>
+    <t>CISNEROS HERNANDEZ JOSE ANDRES</t>
+  </si>
+  <si>
+    <t>CEDILLO GARCIA JOSE DE JESUS</t>
+  </si>
+  <si>
+    <t>LOZA AMEZOLA YOLANDA</t>
+  </si>
+  <si>
+    <t>GOMEZ REYES CARLOS FRANCISCO</t>
+  </si>
+  <si>
+    <t>COVARRUBIAS MATA JUAN LORENZO</t>
+  </si>
+  <si>
+    <t>VAZQUEZ CASTILLO HUGO ENRIQUE</t>
+  </si>
+  <si>
+    <t>RICARDEZ ROJAS ELSA</t>
+  </si>
+  <si>
+    <t>CHAVEZ RESENDIZ EMMANUEL ANTONIO</t>
+  </si>
+  <si>
+    <t>SILVA FERNANDEZ ISAIAS EFREN</t>
+  </si>
+  <si>
+    <t>BARBOSA DE LA CALLEJA CARLOS ALBERTO</t>
+  </si>
+  <si>
+    <t>IZAGUIRRE ECHAVARRIA ERI GUADALUPE</t>
+  </si>
+  <si>
+    <t>DIRECCION MERCADOTECNIA</t>
+  </si>
+  <si>
+    <t>MARTINEZ ARIAS ROLANDO</t>
+  </si>
+  <si>
+    <t>SALDAÑA GONZALEZ MOISES</t>
+  </si>
+  <si>
+    <t>GONZALEZ LOPEZ JOSE ALFONSO</t>
+  </si>
+  <si>
+    <t>SANCHEZ PUENTE HOMERO GUADALUPE</t>
+  </si>
+  <si>
+    <t>SALCEDO SANDOVAL MARIA DE JESUS</t>
+  </si>
+  <si>
+    <t>SECRETARIA DE MARINA</t>
+  </si>
+  <si>
+    <t>VACANTE AGUASCALIENTES</t>
+  </si>
+  <si>
+    <t>VACANTE CONSECIONARIO</t>
+  </si>
+  <si>
+    <t>A6-FRANCISCO VILLA</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ MEDEROS MARISELA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>MARTINEZ CERINO IRVING</t>
+  </si>
+  <si>
+    <t>30-VALLARTA PITILL</t>
+  </si>
+  <si>
+    <t>A7-MISMALOYA</t>
+  </si>
+  <si>
+    <t>CONTRERAS RAMIREZ JOSE ISRAEL</t>
+  </si>
+  <si>
+    <t>24-PUERTO VALLARTA</t>
+  </si>
+  <si>
+    <t>MARISCAL RUVALCABA JONATHAN ALONSO</t>
+  </si>
+  <si>
+    <t>GTH Y DO</t>
+  </si>
+  <si>
+    <t>BAÑUELOS BARRERA CESAR</t>
+  </si>
+  <si>
+    <t>ORTEGA GARCIA CHRISTIAN</t>
+  </si>
+  <si>
+    <t>BERVERA CASTILLO ZAC NICTE</t>
+  </si>
+  <si>
+    <t>DÍAZ BALANDRÁN RUBÉN</t>
+  </si>
+  <si>
+    <t>MERCADOTECNIA</t>
+  </si>
+  <si>
+    <t>ALTAMIRANO BOLAÑOS RAFAEL</t>
+  </si>
+  <si>
+    <t>FIERRO GARZA RAUL</t>
+  </si>
+  <si>
+    <t>SANCHEZ CAMARENA ALBA ELENA</t>
+  </si>
+  <si>
+    <t>INACTIVOS TIENDAS GDL</t>
+  </si>
+  <si>
+    <t>MARTINEZ MICHELLE</t>
+  </si>
+  <si>
+    <t>VALDEZ DAVILA DIEGO</t>
+  </si>
+  <si>
+    <t>HERNANDEZ MENDOZA TONATIUH</t>
+  </si>
+  <si>
+    <t>PATIÑO DIAZ EDGAR SALVADOR</t>
+  </si>
+  <si>
+    <t>GALLEGOS CHAVEZ JUANA</t>
+  </si>
+  <si>
+    <t>GUZMAN AMAYA MARCO ANTONIO</t>
+  </si>
+  <si>
+    <t>MOSTRADOR CD HIDALGO</t>
+  </si>
+  <si>
+    <t>VACANTE SAN LUIS POTOSI</t>
+  </si>
+  <si>
+    <t>CORTES LOPEZ JAVIER</t>
+  </si>
+  <si>
+    <t>CORTEZ LOPEZ JAVIER</t>
+  </si>
+  <si>
+    <t>VENDEDOR ESTANDAR</t>
+  </si>
+  <si>
+    <t>TAMAYO ROSADO WILBERTH GEOVANY</t>
+  </si>
+  <si>
+    <t>ORTEGA CHAROLA MARCOS DE JESUS</t>
+  </si>
+  <si>
+    <t>GARCIA RAMIREZ DAVID</t>
+  </si>
+  <si>
+    <t>GONZALEZ PALOMO ERICK</t>
+  </si>
+  <si>
+    <t>GODINEZ VILLA GUILLERMO</t>
+  </si>
+  <si>
+    <t>GRANO VELARDE GERARDO JUSTINO</t>
+  </si>
+  <si>
+    <t>DIAZ BALANDRAN RUBEN</t>
   </si>
 </sst>
 </file>
@@ -66,12 +475,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -86,8 +501,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -422,16 +838,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CA33032-1A32-4971-BD12-2E0021DF01DE}">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11.1796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.81640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="16.26953125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="71.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -444,8 +861,14 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>50000850</v>
       </c>
@@ -457,6 +880,924 @@
       </c>
       <c r="D2">
         <v>-103.352981</v>
+      </c>
+      <c r="E2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>50000575</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>50000952</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>50000395</v>
+      </c>
+      <c r="B5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>50000378</v>
+      </c>
+      <c r="B6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>50000452</v>
+      </c>
+      <c r="B7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>50000416</v>
+      </c>
+      <c r="B8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" t="s">
+        <v>14</v>
+      </c>
+      <c r="F8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>50000600</v>
+      </c>
+      <c r="B9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" t="s">
+        <v>14</v>
+      </c>
+      <c r="F9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>0</v>
+      </c>
+      <c r="B10" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10" t="s">
+        <v>14</v>
+      </c>
+      <c r="F10" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>50000413</v>
+      </c>
+      <c r="B11" t="s">
+        <v>16</v>
+      </c>
+      <c r="E11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F11" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>50000877</v>
+      </c>
+      <c r="B12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E12" t="s">
+        <v>15</v>
+      </c>
+      <c r="F12" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>50000417</v>
+      </c>
+      <c r="B13" t="s">
+        <v>18</v>
+      </c>
+      <c r="E13" t="s">
+        <v>15</v>
+      </c>
+      <c r="F13" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>50000900</v>
+      </c>
+      <c r="B14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E14" t="s">
+        <v>15</v>
+      </c>
+      <c r="F14" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>50000415</v>
+      </c>
+      <c r="B15" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" t="s">
+        <v>15</v>
+      </c>
+      <c r="F15" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A16">
+        <v>50000461</v>
+      </c>
+      <c r="B16" t="s">
+        <v>21</v>
+      </c>
+      <c r="E16" t="s">
+        <v>15</v>
+      </c>
+      <c r="F16" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>50000410</v>
+      </c>
+      <c r="B17" t="s">
+        <v>22</v>
+      </c>
+      <c r="E17" t="s">
+        <v>15</v>
+      </c>
+      <c r="F17" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <v>50001100</v>
+      </c>
+      <c r="B18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E18" t="s">
+        <v>15</v>
+      </c>
+      <c r="F18" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <v>50000392</v>
+      </c>
+      <c r="B19" t="s">
+        <v>24</v>
+      </c>
+      <c r="E19" t="s">
+        <v>15</v>
+      </c>
+      <c r="F19" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A20">
+        <v>1</v>
+      </c>
+      <c r="B20" t="s">
+        <v>25</v>
+      </c>
+      <c r="E20" t="s">
+        <v>15</v>
+      </c>
+      <c r="F20" t="s">
+        <v>26</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8EBBA353-B886-4BA6-8283-ADD71B628B28}">
+  <dimension ref="C3:C132"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="3" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C4" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C9" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C10" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="11" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C12" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C13" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C14" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C15" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C16" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="17" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C17" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C18" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C19" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="20" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C20" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="21" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C21" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="22" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C22" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="23" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C23" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="24" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C24" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="25" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C25" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="26" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C26" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="27" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C27" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="28" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C28" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C29" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="30" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C30" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="31" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C31" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="32" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C32" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="33" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C33" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="34" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C34" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="35" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C35" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="36" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C36" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="37" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C37" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="38" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C38" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="39" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C39" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="40" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C40" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="41" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C41" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="42" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C42" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="43" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C43" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="44" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C44" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="45" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C45" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="46" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C46" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="47" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C47" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="48" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C48" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="49" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C49" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="50" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C50" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="51" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C51" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="52" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C52" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="53" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C53" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="54" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C54" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="55" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C55" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="56" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C56" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="57" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C57" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="58" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C58" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="59" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C59" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="60" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C60" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="61" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C61" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="62" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C62" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="63" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C63" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="64" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C64" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="65" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C65" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="66" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C66" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="67" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C67" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="68" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C68" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="69" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C69" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="70" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C70" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="71" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C71" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="72" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C72" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="73" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C73" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="74" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C74" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="75" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C75" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="76" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C76" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="77" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C77" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="78" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C78" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="79" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C79" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="80" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C80" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="81" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C81" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="82" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C82" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="83" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C83" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="84" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C84" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="85" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C85" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="86" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C86" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="87" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C87" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="88" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C88" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="89" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C89" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="90" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C90" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="91" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C91" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="92" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C92" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="93" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C93" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="94" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C94" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="95" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C95" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="96" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C96" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="97" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C97" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="98" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C98" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="99" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C99" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="100" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C100" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="101" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C101" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="102" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C102" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="103" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C103" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="104" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C104" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="105" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C105" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="106" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C106" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="107" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C107" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="108" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C108" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="109" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C109" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="110" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C110" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="111" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C111" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="112" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C112" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="113" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C113" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="114" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C114" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="115" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C115" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="116" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C116" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="117" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C117" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="118" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C118" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="119" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C119" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="120" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C120" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="121" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C121" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="122" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C122" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="123" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C123" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="124" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C124" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="125" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C125" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="126" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C126" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="127" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C127" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="128" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C128" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="129" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C129" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="130" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C130" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="131" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C131" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="132" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C132" t="s">
+        <v>140</v>
       </c>
     </row>
   </sheetData>
